--- a/out/Attention-mamba2_repeat_1_000001.xlsx
+++ b/out/Attention-mamba2_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7867500136927614</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.103542575915647</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386750013692762</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-5.756669758725911e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.02478644151927139</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.04963924646850443</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.0957639593566835</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.2164438953364906</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.02945753072326762</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.179473768334904</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.00597610995085539</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.1619234161748735</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.005174115645872323</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.1662902512581174</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.002526964121082358</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0002055102400048636</v>
+        <v>0.166164722101992</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01153181967156795</v>
+        <v>0.001203054272881818</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.01173732991157274</v>
+        <v>0.1660418645222371</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.0004982660235487662</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.01173732991157274</v>
+        <v>0.1658338437499779</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0003437955134918071</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.01173732991157274</v>
+        <v>0.1660229282910768</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.0001406088673481482</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.01194460056990955</v>
+        <v>0.1659598438105695</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>5.294835844601998e-05</v>
+        <v>7.050339205511362e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.003280550605136086</v>
+        <v>0.1659601138893289</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-0.04360832353256121</v>
+        <v>2.491725292766325e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.05549997574402473</v>
+        <v>0.1659386871990606</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>1.103373131740489e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.05570102721375728</v>
+        <v>0.1659363773182503</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>2.905404250635916e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.05869867112941248</v>
+        <v>0.1659311282928672</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.07078071895110351</v>
+        <v>0.1659256413632066</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-0.04340768183163814</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09912119092870202</v>
+        <v>0.1659200628379036</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.09931664931492461</v>
+        <v>0.1659148693431695</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.04153155477543326</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.140848204090358</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.1409920740313355</v>
+        <v>0.1659095415488468</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.01639050550636612</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.1246015685249695</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1247491102191512</v>
+        <v>0.1659096212597913</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-0.003531232186415713</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.1282803424055669</v>
+        <v>0.1659096132886969</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.1282803424055669</v>
+        <v>0.165909772710586</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.1284285947879756</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.06338657394188814</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.001337161451586639</v>
+        <v>0.1659100277856088</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.009285639127232768</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.04634543658103049</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.005671474234879928</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.05008490748397459</v>
+        <v>0.1659097408262082</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.05024806790894479</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.02161136444064463</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.05756861501558381</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0.02331559063216978</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.003308829160140012</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0.02424420428607837</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.02170125490398775</v>
+        <v>0.1659098763348141</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0.007926617742642481</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.01320355261625955</v>
+        <v>0.1659098125660582</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.01037329300359602</v>
+        <v>0.165909772710586</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-0.007570129189928105</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.002591483231321443</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.00276661599357822</v>
+        <v>0.1659095016933745</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.04402757827418174</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.0467941942677598</v>
+        <v>0.1659094219824297</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.04701808470746852</v>
+        <v>0.1659094698089964</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.04355801395665482</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.04049983765836549</v>
+        <v>0.1659095893754135</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01885275036769403</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.03444202507297182</v>
+        <v>0.1659095734332246</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.0108895034891637</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.03727224988315173</v>
+        <v>0.1659095893754135</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.004713238869599534</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.03575778424572362</v>
+        <v>0.1659095734332246</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.003636870630442975</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.03829564819845592</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001816004561498466</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.03828005467471434</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0009055815306648696</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.0382697574518146</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0008846562379435471</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.03913167215726094</v>
+        <v>0.1659097806816804</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0007485125270828819</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.039743042004143</v>
+        <v>0.165909995901231</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0003088761063336218</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03961114050006866</v>
+        <v>0.1659099082191919</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0001347889193828607</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.0395713225952842</v>
+        <v>0.1659098603926252</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>7.368760325912526e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03958331392741553</v>
+        <v>0.1659099082191919</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>1.78634362940114e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.03954522028059361</v>
+        <v>0.1659097248840192</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>6.789986958648115e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.03954089059077925</v>
+        <v>0.1659097328551137</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>9.391472654753699e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.03953622605863866</v>
+        <v>0.1659097408262082</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-1.942849546638614e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.03953139767289709</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.332463389075608e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.03952639127967134</v>
+        <v>0.1659097487973026</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.046808757323663e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.03952162707241252</v>
+        <v>0.1659097886527749</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.618577352593679e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.03951681718879286</v>
+        <v>0.1659098524215308</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-4.507115944527151e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.03951203905563674</v>
+        <v>0.1659099640168531</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.03951208688220346</v>
+        <v>0.1659100118434199</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.03951204702673119</v>
+        <v>0.1659099719879476</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.03951197528688098</v>
+        <v>0.1659099002480975</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.03951209485329792</v>
+        <v>0.1659100198145143</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.0395119354314087</v>
+        <v>0.1659098603926252</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.03951170426966936</v>
+        <v>0.1659096292308858</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.03951165644310252</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.03951168832748046</v>
+        <v>0.1659096132886969</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0395117520962361</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.0395117520962361</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.03951167238529155</v>
+        <v>0.165909597346508</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.03924283718399762</v>
+        <v>0.1659094777800909</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.004514198178158375</v>
+        <v>0.1659094379246186</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.04689113447768468</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1335037515795857</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.05397072321399648</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1943560820563938</v>
+        <v>0.1659097169129248</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.02518976419669493</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1906173425380173</v>
+        <v>0.1659097009707359</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.0112480843235605</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1878508490464035</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.004501803729263018</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1855701208330479</v>
+        <v>0.1659096372019802</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1824297170854013</v>
+        <v>0.1659095335777523</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.07984706288724519</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1009701567996589</v>
+        <v>0.1659094140113352</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1007576240429545</v>
+        <v>0.1659095335777523</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001154432651394123</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1309502914921565</v>
+        <v>0.165909581404319</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.04318560618272278</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1886550868136329</v>
+        <v>0.1659096770574525</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1521566156807679</v>
+        <v>0.1659095574910357</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.0133363872763379</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1591602775987659</v>
+        <v>0.1659095654621301</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000001.xlsx
+++ b/out/Attention-mamba2_repeat_1_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.2857574499049893</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.6160766030030931</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0445617031931145</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.0445617031931145</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.386750013692762</v>
+        <v>0.0445617031931145</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931145</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.6160766030030931</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.6160766030030932</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311455</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931146</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.416076603003093</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.416076603003093</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.416076603003093</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.416076603003093</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.503542575915647</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-7.523055118974298e-06</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.003748044738790219</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.003755567793909227</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.003762409753779531</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.001517291563815178</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.0007154651629056316</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.0007159400597121636</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.386750013692762</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0002055102400048636</v>
+        <v>-0.0008046056437506341</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.01153181967156795</v>
+        <v>0.0003151374703110849</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.503542575915647</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.01173732991157274</v>
+        <v>-0.0008918809062069049</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>8.473658666556224e-05</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.503542575915647</v>
+        <v>-1.076714909199301</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.01173732991157274</v>
+        <v>-0.001038624902687618</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.0001078671666657191</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.4160766030030929</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.01173732991157274</v>
+        <v>-0.0009080879433748778</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>3.130683764770315e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.01194460056990955</v>
+        <v>-0.0009536065141418949</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>5.294835844601998e-05</v>
+        <v>1.504030123183495e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.003280550605136086</v>
+        <v>-0.0009549388409329113</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-0.04360832353256121</v>
+        <v>-6.9568019527284e-07</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.503542575915647</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.05549997574402473</v>
+        <v>-0.0009713216350274161</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>-1.8372730126832e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.05570102721375728</v>
+        <v>-0.0009744342831538524</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>-3.498251797817692e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.05869867112941248</v>
+        <v>-0.0009796064647884341</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>-4.408356481861036e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.07078071895110351</v>
+        <v>-0.0009849314971334534</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-0.04340768183163814</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09912119092870202</v>
+        <v>-0.00116080271591316</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-0.005221272265292802</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.09931664931492461</v>
+        <v>-0.01879973851235723</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.04153155477543326</v>
+        <v>-0.03757049067462127</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.140848204090358</v>
+        <v>-0.04395280478866095</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.1409920740313355</v>
+        <v>-0.04399790896405268</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.01639050550636612</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311471</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.1246015685249695</v>
+        <v>-0.03871614220780192</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.005206148557864337</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1247491102191512</v>
+        <v>-0.0335099537944654</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-0.003531232186415713</v>
+        <v>0.002339419369006314</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.1282803424055669</v>
+        <v>-0.03407552806190669</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>0.003806068233271606</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.1282803424055669</v>
+        <v>-0.02881684742954152</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>0.001109304999232922</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7867500136927614</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.1284285947879756</v>
+        <v>-0.03041455002253491</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.06338657394188814</v>
+        <v>0.002002707691849464</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.001337161451586639</v>
+        <v>-0.02752026744413225</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.009285639127232768</v>
+        <v>0.0004879581313383204</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.103542575915647</v>
+        <v>-1.276714909199301</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.04634543658103049</v>
+        <v>-0.02855105788263003</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.005671474234879928</v>
+        <v>0.0002001591378128167</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.103542575915647</v>
+        <v>-0.616076603003093</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.05008490748397459</v>
+        <v>-0.02863969149713788</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>6.468610281331084e-05</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311475</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.05024806790894479</v>
+        <v>-0.02871126328304026</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>4.840137584973274e-05</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.02161136444064463</v>
+        <v>-0.02867937801491365</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>1.235426112532259e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.05756861501558381</v>
+        <v>-0.02870308498512977</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0.02331559063216978</v>
+        <v>1.047188727039634e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.003308829160140012</v>
+        <v>-0.02869468558241916</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0.02424420428607837</v>
+        <v>5.674156310415546e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.02170125490398775</v>
+        <v>-0.02869350712338474</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0.007926617742642481</v>
+        <v>-6.819975756862222e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.01320355261625955</v>
+        <v>-0.02870062976528483</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-3.159459953747489e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.01037329300359602</v>
+        <v>-0.02870631606218277</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-0.007570129189928105</v>
+        <v>-4.175268326645054e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.2445617031931148</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.002591483231321443</v>
+        <v>-0.0287115355438838</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311471</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.00276661599357822</v>
+        <v>-0.02871277106352523</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.04402757827418174</v>
+        <v>-5.601198883566231e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.0467941942677598</v>
+        <v>-0.02871817298504722</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.386750013692762</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.04701808470746852</v>
+        <v>-0.02888192225710023</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.04355801395665482</v>
+        <v>0.03185755848595028</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.04049983765836549</v>
+        <v>0.03512704573714244</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01885275036769403</v>
+        <v>0.01378856708337302</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.03444202507297182</v>
+        <v>0.03069648076581629</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.0108895034891637</v>
+        <v>0.00796438962148757</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.03727224988315173</v>
+        <v>0.03276644531078381</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.004713238869599534</v>
+        <v>0.003447090493167228</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.03575778424572362</v>
+        <v>0.03165880460239027</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.003636870630442975</v>
+        <v>0.002658748164378381</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.03829564819845592</v>
+        <v>0.03351383528336417</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001816004561498466</v>
+        <v>0.001326874082189191</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.386750013692762</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.03828005467471434</v>
+        <v>0.03350108723044407</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0009055815306648696</v>
+        <v>0.0006610162910102318</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311471</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.0382697574518146</v>
+        <v>0.03349221274295495</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0008846562379435471</v>
+        <v>0.000645824427548535</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311471</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.03913167215726094</v>
+        <v>0.03412128990104107</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0007485125270828819</v>
+        <v>0.0005459666806664526</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.039743042004143</v>
+        <v>0.03456703601104987</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.0003088761063336218</v>
+        <v>0.000224505509505782</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.386750013692762</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03961114050006866</v>
+        <v>0.03446922234493215</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.0001347889193828607</v>
+        <v>9.740803843368347e-05</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.0395713225952842</v>
+        <v>0.03443875011492858</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>7.368760325912526e-05</v>
+        <v>5.22670890385856e-05</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03958331392741553</v>
+        <v>0.03444616385543533</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>1.78634362940114e-05</v>
+        <v>1.17665199489417e-05</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.03954522028059361</v>
+        <v>0.03441689518109931</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>6.789986958648115e-06</v>
+        <v>3.645990436341951e-06</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.03954089059077925</v>
+        <v>0.03441238674190198</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>9.391472654753699e-07</v>
+        <v>-6.806201705633672e-07</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.03953622605863866</v>
+        <v>0.03440763289246196</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-1.942849546638614e-06</v>
+        <v>-2.77661785210081e-06</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.03953139767289709</v>
+        <v>0.03440275987676659</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.332463389075608e-06</v>
+        <v>-3.888308926050405e-06</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.03952639127967134</v>
+        <v>0.03439775561461598</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.046808757323663e-06</v>
+        <v>-4.364539171549108e-06</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.03952162707241252</v>
+        <v>0.03439295266524912</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.03951681718879286</v>
+        <v>0.03438814278162946</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.03951203905563674</v>
+        <v>0.03438336464847333</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.386750013692762</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.03951208688220346</v>
+        <v>0.03438341247504006</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.03951204702673119</v>
+        <v>0.03438337261956779</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.03951197528688098</v>
+        <v>0.03438330087971757</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.386750013692762</v>
+        <v>0.2445617031931147</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.03951209485329792</v>
+        <v>0.03438342044613452</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.0395119354314087</v>
+        <v>0.03438326102424529</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.03951170426966936</v>
+        <v>0.03438302986250596</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.03951165644310252</v>
+        <v>0.03438298203593912</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.03951168832748046</v>
+        <v>0.03438301392031706</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0395117520962361</v>
+        <v>0.0343830776890727</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.0395117520962361</v>
+        <v>0.0343830776890727</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.03951167238529155</v>
+        <v>0.03438299797812815</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.03924283718399762</v>
+        <v>0.03417242109714565</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.004514198178158375</v>
+        <v>0.006971624856536044</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.04689113447768468</v>
+        <v>0.03707465265317391</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1335037515795857</v>
+        <v>0.1086979403420335</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.05397072321399648</v>
+        <v>0.04261076972991783</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1943560820563938</v>
+        <v>0.1566885866399529</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.02518976419669493</v>
+        <v>0.01988919123476444</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1906173425380173</v>
+        <v>0.1537400637801369</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.0112480843235605</v>
+        <v>0.008882640055306212</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1878508490464035</v>
+        <v>0.1515582806800636</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.004501803729263018</v>
+        <v>0.003556263902150153</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1855701208330479</v>
+        <v>0.149759610145336</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1824297170854013</v>
+        <v>0.1474550073147824</v>
       </c>
     </row>
     <row r="121">
@@ -97128,7 +97128,7 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.07984706288724519</v>
+        <v>-0.001401359703327166</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.103542575915647</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1009701567996589</v>
+        <v>0.1447760874132488</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.04456170319311467</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1007576240429545</v>
+        <v>0.1447760874132488</v>
       </c>
     </row>
     <row r="123">
@@ -98718,21 +98718,21 @@
         <v>0</v>
       </c>
       <c r="IY123" t="n">
-        <v>0.001154432651394123</v>
+        <v>0</v>
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7867500136927614</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1309502914921565</v>
+        <v>0.1445657581132806</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.04318560618272278</v>
+        <v>0.02756367849373621</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.386750013692762</v>
+        <v>0.7052000093893221</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1886550868136329</v>
+        <v>0.2000504906317424</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1521566156807679</v>
+        <v>0.1650081912672883</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0.0133363872763379</v>
+        <v>-0.002167848900555702</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.386750013692762</v>
+        <v>0.9052000093893222</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1591602775987659</v>
+        <v>0.1705534937962778</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000001.xlsx
+++ b/out/Attention-mamba2_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01299940794706345</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.2857574499049893</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1334802061319351</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.3699999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.02537131868302822</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6160766030030931</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01333330571651459</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.0445617031931145</v>
+        <v>0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.00448494590818882</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6160766030030932</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1906514316797256</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.0445617031931145</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.03101228922605515</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.0445617031931145</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01645488478243351</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2445617031931145</v>
+        <v>0.16</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.007686148397624493</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6160766030030931</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.02346338704228401</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6160766030030932</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.004727333784103394</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.04456170319311455</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01993231102824211</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.004975411109626293</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2445617031931146</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.1884277611970901</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.416076603003093</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.3670219480991364</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.3963089883327484</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0190549623221159</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.07125211507081985</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.04193238168954849</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0355149507522583</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.03901240229606628</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01710843481123447</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1085616424679756</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.1538480669260025</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.276714909199301</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.00332704046741128</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.005847529508173466</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.416076603003093</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001739923027344048</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.2445617031931147</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.009707819670438766</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.2445617031931147</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.004522622097283602</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.416076603003093</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2939449846744537</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.416076603003093</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.02730401419103146</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.06165804713964462</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.2445617031931148</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.02872228622436523</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.2445617031931148</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.006992936134338379</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.004509668797254562</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01255366485565901</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.005716955754905939</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.2445617031931147</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.01478719711303711</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4160766030030929</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.4438483715057373</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.4314914047718048</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.3716030418872833</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.3135310411453247</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-1.832464563928079e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.007889953300800185</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.2896588742733002</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.01580117777179286</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.03048388960583396</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.1733306795358658</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.523055118974298e-06</v>
+        <v>0.06889896671024384</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.003748044738790219</v>
+        <v>0.00937620908896813</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1521258503198624</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.003755567793909227</v>
+        <v>0.05712971148819337</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.001898719333956945</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.1380800753831863</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.003762409753779531</v>
+        <v>0.05153961946045398</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.001517291563815178</v>
+        <v>0.001643811630141548</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.06750019639730453</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0007154651629056316</v>
+        <v>0.05292642706298525</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0007159400597121636</v>
+        <v>0.0008007204045799818</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.005893219262361526</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0008046056437506341</v>
+        <v>0.052883056390716</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0003151374703110849</v>
+        <v>0.0003798668479977473</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.05593392625451088</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0008918809062069049</v>
+        <v>0.05284051900103851</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>8.473658666556224e-05</v>
+        <v>0.0001553325384757131</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.05048904567956924</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.076714909199301</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.001038624902687618</v>
+        <v>0.05277087536944775</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001078671666657191</v>
+        <v>0.0001061206945637616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01813699305057526</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.4160766030030929</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0009080879433748778</v>
+        <v>0.05282763904710929</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>3.130683764770315e-05</v>
+        <v>4.138866570383483e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.05381901189684868</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2445617031931148</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0009536065141418949</v>
+        <v>0.05280417488827859</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>1.504030123183495e-05</v>
+        <v>1.905417799985921e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.03775019571185112</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2445617031931148</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0009549388409329113</v>
+        <v>0.05280084623303218</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>-6.9568019527284e-07</v>
+        <v>4.447553556104185e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02456890046596527</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2445617031931148</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0009713216350274161</v>
+        <v>0.05279065885715792</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>-1.8372730126832e-06</v>
+        <v>1.536993520230006e-07</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.05327542871236801</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2445617031931148</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0009744342831538524</v>
+        <v>0.05278650816550106</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-3.498251797817692e-06</v>
+        <v>-2.741313071246881e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.06245952472090721</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0009796064647884341</v>
+        <v>0.05278143132175273</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-4.408356481861036e-06</v>
+        <v>-3.934348768804317e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.06635129451751709</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0009849314971334534</v>
+        <v>0.05277626942443685</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.06953469663858414</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.00116080271591316</v>
+        <v>0.05277105305326101</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-0.005221272265292802</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.07021673023700714</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2445617031931147</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.01879973851235723</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.03757049067462127</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0009818969992920756</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2445617031931148</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.04395280478866095</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="62">
@@ -50227,17 +50227,17 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.07433179020881653</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.616076603003093</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.04399790896405268</v>
+        <v>0.05276572514415463</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.02385684102773666</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.04456170319311471</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.03871614220780192</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.005206148557864337</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.0836145356297493</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.0335099537944654</v>
+        <v>0.05276580485509918</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.002339419369006314</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02803652733564377</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.03407552806190669</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.003806068233271606</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.01215591281652451</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.02881684742954152</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.001109304999232922</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.03721841797232628</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.03041455002253491</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002002707691849464</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.05454646050930023</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.02752026744413225</v>
+        <v>0.05276621138091665</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.0004879581313383204</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01533848792314529</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.276714909199301</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.02855105788263003</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0002001591378128167</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.03368256986141205</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.616076603003093</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.02863969149713788</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>6.468610281331084e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.08022525161504745</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.04456170319311475</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.02871126328304026</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>4.840137584973274e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.07125911861658096</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.02867937801491365</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>1.235426112532259e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.08527040481567383</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.02870308498512977</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.047188727039634e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.05225593224167824</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.02869468558241916</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.674156310415546e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.04200217127799988</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.02869350712338474</v>
+        <v>0.05276605993012199</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-6.819975756862222e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.07933523505926132</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.02870062976528483</v>
+        <v>0.05276599616136612</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-3.159459953747489e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.05898681655526161</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.2445617031931147</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.02870631606218277</v>
+        <v>0.05276595630589383</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-4.175268326645054e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01249319314956665</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.2445617031931148</v>
+        <v>-0.3</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.0287115355438838</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.07803662121295929</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.04456170319311471</v>
+        <v>-0.3</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.02871277106352523</v>
+        <v>0.05276568528868235</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-5.601198883566231e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.03222503513097763</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.02871817298504722</v>
+        <v>0.05276560557773756</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.04187734425067902</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.02888192225710023</v>
+        <v>0.05276565340430429</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.03185755848595028</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02357817441225052</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.03512704573714244</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.01378856708337302</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.06499152630567551</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.03069648076581629</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.00796438962148757</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05904445052146912</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.03276644531078381</v>
+        <v>0.05276577297072136</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.003447090493167228</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.06921137869358063</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.03165880460239027</v>
+        <v>0.05276575702853245</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.002658748164378381</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.06031534075737</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.03351383528336417</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.001326874082189191</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.02133429050445557</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.04456170319311467</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.03350108723044407</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.0006610162910102318</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01398024708032608</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.04456170319311471</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.03349221274295495</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.000645824427548535</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.07661972194910049</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.04456170319311471</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.03412128990104107</v>
+        <v>0.05276596427698829</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.0005459666806664526</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.021474439650774</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.03456703601104987</v>
+        <v>0.05276617949653883</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.000224505509505782</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.08067932724952698</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.03446922234493215</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>9.740803843368347e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06045672297477722</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.03443875011492858</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>5.22670890385856e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.06872054189443588</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.03444616385543533</v>
+        <v>0.05276609181449982</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>1.17665199489417e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.04015490412712097</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.03441689518109931</v>
+        <v>0.05276590847932711</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>3.645990436341951e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.03782939165830612</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.03441238674190198</v>
+        <v>0.05276591645042156</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-6.806201705633672e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.06002524495124817</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.03440763289246196</v>
+        <v>0.05276592442151602</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>-2.77661785210081e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.02245408296585083</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.03440275987676659</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>-3.888308926050405e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.02905921638011932</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.04456170319311467</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.03439775561461598</v>
+        <v>0.05276593239261047</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>-4.364539171549108e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.001649245503358543</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.04456170319311467</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.03439295266524912</v>
+        <v>0.05276597224808275</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-4.618577352593679e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.07064399123191833</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.04456170319311467</v>
+        <v>-0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.03438814278162946</v>
+        <v>0.05276603601683862</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-4.507115944527151e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.05873352289199829</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.03438336464847333</v>
+        <v>0.052766147612161</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.06886847317218781</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.03438341247504006</v>
+        <v>0.05276619543872774</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.06663983315229416</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.03438337261956779</v>
+        <v>0.05276615558325546</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.06604626774787903</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.03438330087971757</v>
+        <v>0.05276608384340536</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.05906709283590317</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2445617031931147</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.03438342044613452</v>
+        <v>0.05276620340982219</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.03824586421251297</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.04456170319311467</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.03438326102424529</v>
+        <v>0.05276604398793308</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.08088287711143494</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.04456170319311467</v>
+        <v>0.3</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.03438302986250596</v>
+        <v>0.05276581282619364</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06826957315206528</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.03438298203593912</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0334923192858696</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.03438301392031706</v>
+        <v>0.05276579688400473</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.06710202246904373</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.0343830776890727</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.02421713620424271</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.0343830776890727</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.02478378266096115</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.03438299797812815</v>
+        <v>0.05276578094181581</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.04275117814540863</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.03417242109714565</v>
+        <v>0.05276566137539875</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03476866334676743</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.006971624856536044</v>
+        <v>0.05276562151992647</v>
       </c>
     </row>
     <row r="115">
@@ -92358,7 +92358,7 @@
         <v>0</v>
       </c>
       <c r="IY115" t="n">
-        <v>0.03707465265317391</v>
+        <v>0</v>
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.06703165173530579</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1086979403420335</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="116">
@@ -93153,7 +93153,7 @@
         <v>0</v>
       </c>
       <c r="IY116" t="n">
-        <v>0.04261076972991783</v>
+        <v>0</v>
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.04506313800811768</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9052000093893222</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1566885866399529</v>
+        <v>0.05276590050823265</v>
       </c>
     </row>
     <row r="117">
@@ -93948,7 +93948,7 @@
         <v>0</v>
       </c>
       <c r="IY117" t="n">
-        <v>0.01988919123476444</v>
+        <v>0</v>
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01875279098749161</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1537400637801369</v>
+        <v>0.05276588456604374</v>
       </c>
     </row>
     <row r="118">
@@ -94743,7 +94743,7 @@
         <v>0</v>
       </c>
       <c r="IY118" t="n">
-        <v>0.008882640055306212</v>
+        <v>0</v>
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.03613370656967163</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1515582806800636</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="119">
@@ -95538,7 +95538,7 @@
         <v>0</v>
       </c>
       <c r="IY119" t="n">
-        <v>0.003556263902150153</v>
+        <v>0</v>
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.04581314325332642</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7052000093893221</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.149759610145336</v>
+        <v>0.05276582079728809</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.05286576598882675</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.04456170319311467</v>
+        <v>0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1474550073147824</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="121">
@@ -97128,21 +97128,21 @@
         <v>0</v>
       </c>
       <c r="IY121" t="n">
-        <v>-0.001401359703327166</v>
+        <v>0</v>
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.03040208667516708</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.04456170319311467</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1447760874132488</v>
+        <v>0.0527655976066431</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.07138288766145706</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.04456170319311467</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1447760874132488</v>
+        <v>0.05276571717306017</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.07423725724220276</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1445657581132806</v>
+        <v>0.0527657649996269</v>
       </c>
     </row>
     <row r="124">
@@ -99513,7 +99513,7 @@
         <v>0</v>
       </c>
       <c r="IY124" t="n">
-        <v>0.02756367849373621</v>
+        <v>0</v>
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.04306212067604065</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7052000093893221</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2000504906317424</v>
+        <v>0.05276586065276037</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.05560789257287979</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.2999999999999994</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1650081912672883</v>
+        <v>0.05276574108634353</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-0.002167848900555702</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01266292482614517</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9052000093893222</v>
+        <v>0.0199999999999993</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.1705534937962778</v>
+        <v>0.05276574905743799</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000001.xlsx
+++ b/out/Attention-mamba2_repeat_1_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.01299940794706345</v>
+        <v>0.01299837045371532</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.5799999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1334802061319351</v>
+        <v>-0.1334838569164276</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.3699999999999999</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.02537131868302822</v>
+        <v>0.02543851546943188</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.16</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.01333330571651459</v>
+        <v>-0.01333724334836006</v>
       </c>
       <c r="JB5" t="n">
         <v>0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.00448494590818882</v>
+        <v>0.004483567085117102</v>
       </c>
       <c r="JB6" t="n">
         <v>0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1906514316797256</v>
+        <v>-0.1906546801328659</v>
       </c>
       <c r="JB7" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.03101228922605515</v>
+        <v>0.03101014159619808</v>
       </c>
       <c r="JB8" t="n">
         <v>0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.01645488478243351</v>
+        <v>0.01645314320921898</v>
       </c>
       <c r="JB9" t="n">
         <v>0.16</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.007686148397624493</v>
+        <v>-0.007688418496400118</v>
       </c>
       <c r="JB10" t="n">
         <v>0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.02346338704228401</v>
+        <v>-0.02346770465373993</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.004727333784103394</v>
+        <v>0.004726251121610403</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.01993231102824211</v>
+        <v>0.01993101835250854</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.4399999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.004975411109626293</v>
+        <v>0.004975107498466969</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.1884277611970901</v>
+        <v>-0.1884306520223618</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.3670219480991364</v>
+        <v>-0.3670248985290527</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.3963089883327484</v>
+        <v>-0.3963117599487305</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0190549623221159</v>
+        <v>-0.01905675232410431</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.07125211507081985</v>
+        <v>-0.07125471532344818</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.04193238168954849</v>
+        <v>-0.04193466901779175</v>
       </c>
       <c r="JB20" t="n">
         <v>0.7199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.0355149507522583</v>
+        <v>-0.03551881015300751</v>
       </c>
       <c r="JB21" t="n">
         <v>0.8599999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.03901240229606628</v>
+        <v>-0.03901602327823639</v>
       </c>
       <c r="JB22" t="n">
         <v>0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.01710843481123447</v>
+        <v>-0.01710767857730389</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1085616424679756</v>
+        <v>-0.1085628941655159</v>
       </c>
       <c r="JB24" t="n">
         <v>0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.1538480669260025</v>
+        <v>-0.1538493782281876</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.00332704046741128</v>
+        <v>-0.003328784834593534</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.005847529508173466</v>
+        <v>-0.005849322769790888</v>
       </c>
       <c r="JB27" t="n">
         <v>0.1199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001739923027344048</v>
+        <v>0.001738428720273077</v>
       </c>
       <c r="JB28" t="n">
         <v>0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.009707819670438766</v>
+        <v>0.009715627878904343</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.004522622097283602</v>
+        <v>-0.004524036776274443</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2939449846744537</v>
+        <v>-0.2939468622207642</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.02730401419103146</v>
+        <v>0.02730295993387699</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.06165804713964462</v>
+        <v>-0.06165853142738342</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.02000000000000007</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.02872228622436523</v>
+        <v>0.02872545830905437</v>
       </c>
       <c r="JB34" t="n">
         <v>0.8599999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.006992936134338379</v>
+        <v>0.007030893582850695</v>
       </c>
       <c r="JB35" t="n">
         <v>0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.004509668797254562</v>
+        <v>0.004511016886681318</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.01255366485565901</v>
+        <v>0.01255340501666069</v>
       </c>
       <c r="JB37" t="n">
         <v>0.7199999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.005716955754905939</v>
+        <v>0.005715409759432077</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.01478719711303711</v>
+        <v>-0.01478897593915462</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.4438483715057373</v>
+        <v>-0.4438508749008179</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.4314914047718048</v>
+        <v>-0.4314941167831421</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.3716030418872833</v>
+        <v>-0.3716045618057251</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.3135310411453247</v>
+        <v>-0.3135283291339874</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.2896588742733002</v>
+        <v>-0.289655327796936</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.1733306795358658</v>
+        <v>-0.1733262836933136</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1521258503198624</v>
+        <v>-0.1521222740411758</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.1380800753831863</v>
+        <v>-0.1380783021450043</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.06750019639730453</v>
+        <v>-0.06751450896263123</v>
       </c>
       <c r="JB48" t="n">
         <v>0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.005893219262361526</v>
+        <v>0.005893263500183821</v>
       </c>
       <c r="JB49" t="n">
         <v>0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.05593392625451088</v>
+        <v>-0.05594465509057045</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.05048904567956924</v>
+        <v>-0.05048859864473343</v>
       </c>
       <c r="JB51" t="n">
         <v>0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.01813699305057526</v>
+        <v>-0.01813673973083496</v>
       </c>
       <c r="JB52" t="n">
         <v>0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.05381901189684868</v>
+        <v>0.05381911247968674</v>
       </c>
       <c r="JB53" t="n">
         <v>0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.03775019571185112</v>
+        <v>0.03775005415081978</v>
       </c>
       <c r="JB54" t="n">
         <v>0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.02456890046596527</v>
+        <v>-0.02456869930028915</v>
       </c>
       <c r="JB55" t="n">
         <v>0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.05327542871236801</v>
+        <v>0.05324617028236389</v>
       </c>
       <c r="JB56" t="n">
         <v>0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.06245952472090721</v>
+        <v>0.06245730072259903</v>
       </c>
       <c r="JB57" t="n">
         <v>0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.06635129451751709</v>
+        <v>0.06634993106126785</v>
       </c>
       <c r="JB58" t="n">
         <v>0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.06953469663858414</v>
+        <v>0.06953351199626923</v>
       </c>
       <c r="JB59" t="n">
         <v>0.2599999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.07021673023700714</v>
+        <v>0.07021576166152954</v>
       </c>
       <c r="JB60" t="n">
         <v>0.2599999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0009818969992920756</v>
+        <v>-0.0009814429795369506</v>
       </c>
       <c r="JB61" t="n">
         <v>0.1199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.07433179020881653</v>
+        <v>0.07433035969734192</v>
       </c>
       <c r="JB62" t="n">
         <v>0.1199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.02385684102773666</v>
+        <v>-0.02385644614696503</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.0836145356297493</v>
+        <v>0.08361247181892395</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.02000000000000007</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.02803652733564377</v>
+        <v>-0.02803613245487213</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.16</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.01215591281652451</v>
+        <v>-0.01215620338916779</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.03721841797232628</v>
+        <v>0.03721857070922852</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.05454646050930023</v>
+        <v>-0.05454736948013306</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.01533848792314529</v>
+        <v>-0.01533842086791992</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.03368256986141205</v>
+        <v>-0.03368210792541504</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.08022525161504745</v>
+        <v>0.08022304624319077</v>
       </c>
       <c r="JB71" t="n">
         <v>0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.07125911861658096</v>
+        <v>0.07125809788703918</v>
       </c>
       <c r="JB72" t="n">
         <v>0.8599999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.08527040481567383</v>
+        <v>0.08526965975761414</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.05225593224167824</v>
+        <v>0.05226786807179451</v>
       </c>
       <c r="JB74" t="n">
         <v>0.8599999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.04200217127799988</v>
+        <v>0.04199905321002007</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.07933523505926132</v>
+        <v>0.07933309674263</v>
       </c>
       <c r="JB76" t="n">
         <v>0.4399999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.05898681655526161</v>
+        <v>0.05898476764559746</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.16</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.01249319314956665</v>
+        <v>-0.01249279081821442</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.3</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.07803662121295929</v>
+        <v>0.07803471386432648</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.3</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.03222503513097763</v>
+        <v>0.03222258388996124</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.4399999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.04187734425067902</v>
+        <v>0.04187490046024323</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.16</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.02357817441225052</v>
+        <v>0.02357557415962219</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.06499152630567551</v>
+        <v>0.06498975306749344</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.16</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.05904445052146912</v>
+        <v>0.05904257297515869</v>
       </c>
       <c r="JB84" t="n">
         <v>0.5799999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.06921137869358063</v>
+        <v>0.06920989602804184</v>
       </c>
       <c r="JB85" t="n">
         <v>0.5799999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.06031534075737</v>
+        <v>0.06031344830989838</v>
       </c>
       <c r="JB86" t="n">
         <v>0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.02133429050445557</v>
+        <v>0.0213320329785347</v>
       </c>
       <c r="JB87" t="n">
         <v>0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.01398024708032608</v>
+        <v>-0.01398520916700363</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.07661972194910049</v>
+        <v>0.07661723345518112</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.021474439650774</v>
+        <v>0.02146529406309128</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.08067932724952698</v>
+        <v>0.08067636936903</v>
       </c>
       <c r="JB91" t="n">
         <v>0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06045672297477722</v>
+        <v>0.06045512855052948</v>
       </c>
       <c r="JB92" t="n">
         <v>0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.06872054189443588</v>
+        <v>0.06871974468231201</v>
       </c>
       <c r="JB93" t="n">
         <v>0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.04015490412712097</v>
+        <v>0.04015262424945831</v>
       </c>
       <c r="JB94" t="n">
         <v>0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.03782939165830612</v>
+        <v>0.03782723844051361</v>
       </c>
       <c r="JB95" t="n">
         <v>0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.06002524495124817</v>
+        <v>0.06002341955900192</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.5799999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.02245408296585083</v>
+        <v>0.0224517285823822</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.02905921638011932</v>
+        <v>0.02905729413032532</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.5799999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.001649245503358543</v>
+        <v>-0.001648754230700433</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.07064399123191833</v>
+        <v>0.07064273208379745</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.3</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.05873352289199829</v>
+        <v>0.05873291194438934</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.02000000000000007</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.06886847317218781</v>
+        <v>0.06886672973632812</v>
       </c>
       <c r="JB102" t="n">
         <v>0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.06663983315229416</v>
+        <v>0.0666392520070076</v>
       </c>
       <c r="JB103" t="n">
         <v>0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.06604626774787903</v>
+        <v>0.06604559719562531</v>
       </c>
       <c r="JB104" t="n">
         <v>0.5799999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.05906709283590317</v>
+        <v>0.05906675755977631</v>
       </c>
       <c r="JB105" t="n">
         <v>0.5799999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.03824586421251297</v>
+        <v>-0.03831093013286591</v>
       </c>
       <c r="JB106" t="n">
         <v>0.5799999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.08088287711143494</v>
+        <v>0.08088071644306183</v>
       </c>
       <c r="JB107" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06826957315206528</v>
+        <v>0.06826775521039963</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0334923192858696</v>
+        <v>0.03348977863788605</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.1600000000000001</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.06710202246904373</v>
+        <v>0.0671001672744751</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.02421713620424271</v>
+        <v>0.02421478927135468</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.5799999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.02478378266096115</v>
+        <v>0.0247814953327179</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.04275117814540863</v>
+        <v>0.0427488386631012</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.03476866334676743</v>
+        <v>0.03476627916097641</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.5799999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.06703165173530579</v>
+        <v>0.06702996045351028</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.5799999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.04506313800811768</v>
+        <v>0.04506106674671173</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01875279098749161</v>
+        <v>0.01875043660402298</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.5799999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.03613370656967163</v>
+        <v>0.03613156825304031</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.04581314325332642</v>
+        <v>0.04581116884946823</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.05286576598882675</v>
+        <v>0.05285752564668655</v>
       </c>
       <c r="JB120" t="n">
         <v>0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.03040208667516708</v>
+        <v>-0.03040149807929993</v>
       </c>
       <c r="JB121" t="n">
         <v>0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.07138288766145706</v>
+        <v>0.07137984037399292</v>
       </c>
       <c r="JB122" t="n">
         <v>0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.07423725724220276</v>
+        <v>0.07423593103885651</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.04306212067604065</v>
+        <v>0.04305979609489441</v>
       </c>
       <c r="JB124" t="n">
         <v>0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.05560789257287979</v>
+        <v>0.05560611188411713</v>
       </c>
       <c r="JB125" t="n">
         <v>0.2999999999999994</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.01266292482614517</v>
+        <v>0.01266296952962875</v>
       </c>
       <c r="JB126" t="n">
         <v>0.0199999999999993</v>
